--- a/01-Projects/AI-릴스-자동화/촬영용/5편 촬영용 가상 자금일보 (10월 15일).xlsx
+++ b/01-Projects/AI-릴스-자동화/촬영용/5편 촬영용 가상 자금일보 (10월 15일).xlsx
@@ -657,17 +657,17 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>국민</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>****1234</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>운영자금</t>
         </is>
